--- a/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/may-2026.xlsx
+++ b/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/may-2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M60"/>
+  <dimension ref="A1:M57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -565,11 +565,11 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>12063854.88</v>
+        <v>13439.56</v>
       </c>
     </row>
     <row r="3">
@@ -626,11 +626,11 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>35605315.1</v>
+        <v>39665.57</v>
       </c>
     </row>
     <row r="4">
@@ -687,11 +687,11 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>8819451.25</v>
+        <v>9825.18</v>
       </c>
     </row>
     <row r="5">
@@ -748,11 +748,11 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>6707909.88</v>
+        <v>7472.85</v>
       </c>
     </row>
     <row r="6">
@@ -809,11 +809,11 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>7964955.6</v>
+        <v>8873.24</v>
       </c>
     </row>
     <row r="7">
@@ -870,17 +870,17 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>14787113.18</v>
+        <v>16473.36</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1284073-21-CM26</t>
+          <t>1057370-271-CM26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -905,43 +905,43 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>61.602.040-4</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>HOSPITAL PSIQUIATRICO DR. PHILIPPE PINEL PUTAENDO</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>STATUS SPA</t>
+          <t>IGMA CONSULTORES LIMITADA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>77.393.671-4</t>
+          <t>76.465.697-0</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>10216493.4</v>
+        <v>7056.31</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2427-392-CM26</t>
+          <t>1284073-21-CM26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -961,48 +961,48 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>69.060.900-2</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALPARAISO</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>JUEGOS MAGICOS</t>
+          <t>STATUS SPA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>76.102.918-5</t>
+          <t>77.393.671-4</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>8845664.24</v>
+        <v>11381.53</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1057370-271-CM26</t>
+          <t>2427-392-CM26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1022,17 +1022,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>61.602.040-4</t>
+          <t>69.060.900-2</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>HOSPITAL PSIQUIATRICO DR. PHILIPPE PINEL PUTAENDO</t>
+          <t>I MUNICIPALIDAD DE VALPARAISO</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,22 +1042,22 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>IGMA CONSULTORES LIMITADA</t>
+          <t>JUEGOS MAGICOS</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>76.465.697-0</t>
+          <t>76.102.918-5</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>6334013</v>
+        <v>9854.379999999999</v>
       </c>
     </row>
     <row r="11">
@@ -1114,11 +1114,11 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>26417753.18</v>
+        <v>29430.3</v>
       </c>
     </row>
     <row r="12">
@@ -1175,11 +1175,11 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>5053454</v>
+        <v>5629.72</v>
       </c>
     </row>
     <row r="13">
@@ -1236,17 +1236,17 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>10470751.2</v>
+        <v>11664.78</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2175-173-CM26</t>
+          <t>5510-50-CM26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1271,43 +1271,43 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>JUEGOS MAGICOS</t>
+          <t>EASTON LIMITADA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>76.102.918-5</t>
+          <t>76.028.554-4</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>5855696</v>
+        <v>14656.88</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>5510-50-CM26</t>
+          <t>2175-173-CM26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1332,43 +1332,43 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>EASTON LIMITADA</t>
+          <t>JUEGOS MAGICOS</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>76.028.554-4</t>
+          <t>76.102.918-5</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>13156571.15</v>
+        <v>6523.45</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1471-38-CM26</t>
+          <t>5153-829-CM26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1393,43 +1393,43 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>61.104.000-8</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
+          <t>96.882.140-7</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>6570128.55</v>
+        <v>23066.26</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2279-246-CM26</t>
+          <t>2177-50-CM26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1449,48 +1449,48 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>69.071.100-1</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE PUDAHUEL</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>77.018.060-0</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>12495000</v>
+        <v>12310.94</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1426099-86-CM26</t>
+          <t>4034-206-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1510,48 +1510,48 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>69.160.501-9</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>Ilustre Municipalidad de Cañete - Educación</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>ENILDA TERESA FIGUEROA MELLADO</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>6.189.318-0</t>
+          <t>96.882.140-7</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>8314500</v>
+        <v>16310.24</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>5153-829-CM26</t>
+          <t>1432083-1012-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1571,22 +1571,22 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>Servicio local de educación pública de Valdivia</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1602,17 +1602,17 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>20705148.94</v>
+        <v>13485.71</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>4034-206-CM26</t>
+          <t>1426099-86-CM26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1632,48 +1632,48 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>69.160.501-9</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Cañete - Educación</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>ENILDA TERESA FIGUEROA MELLADO</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>6.189.318-0</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>14640690.4</v>
+        <v>9262.639999999999</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2177-50-CM26</t>
+          <t>1471-38-CM26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1698,43 +1698,43 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>61.104.000-8</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>77.018.060-0</t>
+          <t>77.324.357-3</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>11050765</v>
+        <v>7319.35</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1432083-1012-CM26</t>
+          <t>2279-246-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1759,43 +1759,43 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>69.071.100-1</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PUDAHUEL</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>12105283.4</v>
+        <v>13919.87</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2179-102-CM26</t>
+          <t>3708-167-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1815,17 +1815,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>69.191.300-7</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>I MUNICIPALIDAD DE PITRUFQUEN</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1835,28 +1835,28 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>77.324.357-3</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>6693988</v>
+        <v>7498.34</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>5512-87-CM26</t>
+          <t>2179-102-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1876,22 +1876,22 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1907,17 +1907,17 @@
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>9304620.779999999</v>
+        <v>7457.34</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>4803-121-CM26</t>
+          <t>5512-87-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1942,43 +1942,43 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>60.201.000-7</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>SENADO DE LA REPUBLICA</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>77.018.060-0</t>
+          <t>96.882.140-7</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>8497611.5</v>
+        <v>10365.67</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1475044-49-CM26</t>
+          <t>4803-121-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2003,43 +2003,43 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>60.201.000-7</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>SENADO DE LA REPUBLICA</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>INTERGROUPE S.A.</t>
+          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>76.719.470-6</t>
+          <t>77.018.060-0</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>13258628.95</v>
+        <v>9466.639999999999</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>3708-167-CM26</t>
+          <t>1475044-49-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2064,37 +2064,37 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>69.191.300-7</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PITRUFQUEN</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>INTERGROUPE S.A.</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
+          <t>76.719.470-6</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>6730793.85</v>
+        <v>14770.58</v>
       </c>
     </row>
     <row r="28">
@@ -2151,17 +2151,17 @@
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>8844331.439999999</v>
+        <v>9852.889999999999</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>188-253-CM26</t>
+          <t>1426098-122-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2181,48 +2181,48 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>70.933.700-9</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE EDUC SALUD CULTURA Y RECREACION DE LA FLORIDA</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE MUEBLES HP LIMITADA</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>76.058.118-6</t>
+          <t>77.324.357-3</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>16550366.15</v>
+        <v>18887.13</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1426098-122-CM26</t>
+          <t>188-253-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2242,48 +2242,48 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>70.933.700-9</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>CORP MUNICIPAL DE EDUC SALUD CULTURA Y RECREACION DE LA FLORIDA</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>COMERCIALIZADORA DE MUEBLES HP LIMITADA</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
+          <t>76.058.118-6</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>16953799.95</v>
+        <v>18437.69</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2176-246-CM26</t>
+          <t>1214102-927-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2308,17 +2308,17 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>70.835.200-4</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE PUDAHUEL</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2334,17 +2334,17 @@
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>17396164.24</v>
+        <v>41730.15</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1214102-927-CM26</t>
+          <t>2176-246-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2369,17 +2369,17 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>70.835.200-4</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE PUDAHUEL</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2395,11 +2395,11 @@
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>37458565.48</v>
+        <v>19379.94</v>
       </c>
     </row>
     <row r="33">
@@ -2456,11 +2456,11 @@
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>8545600</v>
+        <v>9520.1</v>
       </c>
     </row>
     <row r="34">
@@ -2517,11 +2517,11 @@
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>10502660</v>
+        <v>11700.33</v>
       </c>
     </row>
     <row r="35">
@@ -2578,11 +2578,11 @@
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>13423500</v>
+        <v>14954.25</v>
       </c>
     </row>
     <row r="36">
@@ -2639,11 +2639,11 @@
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>8240478.85</v>
+        <v>9180.18</v>
       </c>
     </row>
     <row r="37">
@@ -2700,11 +2700,11 @@
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>7200114.55</v>
+        <v>8021.18</v>
       </c>
     </row>
     <row r="38">
@@ -2761,11 +2761,11 @@
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>25807911.92</v>
+        <v>28750.92</v>
       </c>
     </row>
     <row r="39">
@@ -2822,11 +2822,11 @@
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>16764980.95</v>
+        <v>18676.77</v>
       </c>
     </row>
     <row r="40">
@@ -2883,11 +2883,11 @@
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>25498822.75</v>
+        <v>28406.58</v>
       </c>
     </row>
     <row r="41">
@@ -2944,11 +2944,11 @@
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>34000000</v>
+        <v>37877.19</v>
       </c>
     </row>
     <row r="42">
@@ -3005,17 +3005,17 @@
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>11260244.1</v>
+        <v>12544.31</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2328-549-CM26</t>
+          <t>2328-554-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3066,17 +3066,17 @@
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>6795495</v>
+        <v>11227.9</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2328-554-CM26</t>
+          <t>2328-549-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3127,11 +3127,11 @@
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>10078587</v>
+        <v>7570.42</v>
       </c>
     </row>
     <row r="45">
@@ -3188,11 +3188,11 @@
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>10871622.16</v>
+        <v>12111.37</v>
       </c>
     </row>
     <row r="46">
@@ -3249,11 +3249,11 @@
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>6370022.4</v>
+        <v>7096.43</v>
       </c>
     </row>
     <row r="47">
@@ -3310,11 +3310,11 @@
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>95638726.26000001</v>
+        <v>106544.88</v>
       </c>
     </row>
     <row r="48">
@@ -3371,11 +3371,11 @@
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>14994043.12</v>
+        <v>16703.89</v>
       </c>
     </row>
     <row r="49">
@@ -3432,17 +3432,17 @@
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>9260510</v>
+        <v>10316.53</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2291-889-CM26</t>
+          <t>1079650-29-SE26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3457,53 +3457,57 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Cancelada por Comprador</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>61.607.100-9</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>SERVICIO DE SALUD CONCEPCION</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>BLUEMEDICAL SPA</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr"/>
+          <t>76.116.604-2</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>10533987.66</v>
+        <v>12338.38</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1079650-29-SE26</t>
+          <t>1426103-41-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3523,52 +3527,48 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>61.607.100-9</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CONCEPCION</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>BLUEMEDICAL SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>76.116.604-2</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>11075400.21</v>
+        <v>13001.7</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1426103-41-CM26</t>
+          <t>3179-148-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3588,48 +3588,48 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>JUEGOS MAGICOS</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>76.102.918-5</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>11670820</v>
+        <v>17109.45</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>3179-148-CM26</t>
+          <t>5394-255-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3654,43 +3654,43 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>71.133.700-8</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>UNIVERSIDAD DE MAGALLANES</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Magallanes y Antártica</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>JUEGOS MAGICOS</t>
+          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>76.102.918-5</t>
+          <t>77.018.060-0</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>15358091.56</v>
+        <v>13975.49</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1069417-565-CM26</t>
+          <t>2446-603-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3710,48 +3710,48 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Cancelada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>69.270.200-k</t>
+          <t>69.040.300-5</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dirección  de Salud Municipal Chillán</t>
+          <t>I MUNICIPALIDAD DE COQUIMBO</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>JUEGOS MAGICOS</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
+          <t>76.102.918-5</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>7370990.9</v>
+        <v>46477.6</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>5394-255-CM26</t>
+          <t>5510-55-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3776,43 +3776,43 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>71.133.700-8</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE MAGALLANES</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>77.018.060-0</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>12544926.45</v>
+        <v>27266.56</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2446-603-CM26</t>
+          <t>5510-54-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3827,53 +3827,53 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>69.040.300-5</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COQUIMBO</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>JUEGOS MAGICOS</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>76.102.918-5</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>41720052.36</v>
+        <v>31613.93</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1471-44-CM26</t>
+          <t>1471-45-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3893,7 +3893,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>No aceptada</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -3913,205 +3913,22 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE MUEBLES HP LIMITADA</t>
+          <t>STATUS SPA</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>76.058.118-6</t>
+          <t>77.393.671-4</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>5344766</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>5510-54-CM26</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>2239-4-LR25</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>may-2026</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>60.910.000-1</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>UNIVERSIDAD DE CHILE</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>EVENTAIL SPA</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>76.710.414-6</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>CLP</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="n">
-        <v>28377861.96</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>5510-55-CM26</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>2239-4-LR25</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>may-2026</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>60.910.000-1</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>UNIVERSIDAD DE CHILE</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>EVENTAIL SPA</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>76.710.414-6</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>CLP</t>
-        </is>
-      </c>
-      <c r="M59" s="2" t="n">
-        <v>24475500</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>1471-45-CM26</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>2239-4-LR25</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>may-2026</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>61.104.000-8</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Coquimbo</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>STATUS SPA</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>77.393.671-4</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>CLP</t>
-        </is>
-      </c>
-      <c r="M60" s="2" t="n">
-        <v>12039410.2</v>
+        <v>13412.32</v>
       </c>
     </row>
   </sheetData>
